--- a/6.Gerenciamento de Projeto/CONIM - Planejamento e Controle do Projeto.xlsx
+++ b/6.Gerenciamento de Projeto/CONIM - Planejamento e Controle do Projeto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rosag\Documents\CONIM_ContractImovel\6.Gerenciamento de Projeto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42FFE0CB-1F18-4E67-8815-B752DA02D14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D2E6A61-7F05-4E19-BD6D-24CD18214F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -990,7 +990,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="253">
   <si>
     <t>Equipe</t>
   </si>
@@ -1555,9 +1555,6 @@
     <t>26/092025</t>
   </si>
   <si>
-    <t>Em execução</t>
-  </si>
-  <si>
     <t>Material de Suporte e Treinamento</t>
   </si>
   <si>
@@ -1876,7 +1873,7 @@
     <numFmt numFmtId="170" formatCode="#,##0.0&quot; &quot;;&quot;-&quot;#,##0.0&quot; &quot;;&quot; -&quot;#&quot; &quot;;@&quot; &quot;"/>
     <numFmt numFmtId="171" formatCode="#,##0&quot; &quot;;&quot;-&quot;#,##0&quot; &quot;;&quot; -&quot;#&quot; &quot;;@&quot; &quot;"/>
   </numFmts>
-  <fonts count="47" x14ac:knownFonts="1">
+  <fonts count="45" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2110,24 +2107,9 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF1155CC"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -2510,7 +2492,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="193">
+  <cellXfs count="191">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2848,40 +2830,34 @@
     <xf numFmtId="0" fontId="39" fillId="16" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="17" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="40" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="17" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="40" fillId="16" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="16" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="40" fillId="16" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="41" fillId="16" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="41" fillId="16" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="43" fillId="16" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="42" fillId="16" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="16" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="16" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="44" fillId="16" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="16" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="17" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="17" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="23" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2945,24 +2921,6 @@
     <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="20" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="18" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2978,6 +2936,24 @@
     <xf numFmtId="164" fontId="19" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="19" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3017,18 +2993,26 @@
     <xf numFmtId="164" fontId="37" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="32" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="32" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="32" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF666699"/>
@@ -4656,11 +4640,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="149" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="153"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="151"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -4686,11 +4670,11 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="154" t="s">
+      <c r="A2" s="152" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="152"/>
-      <c r="C2" s="153"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="151"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -11666,22 +11650,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="155" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
       <c r="E1" s="5"/>
-      <c r="F1" s="159" t="s">
+      <c r="F1" s="157" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="160"/>
-      <c r="H1" s="160"/>
-      <c r="I1" s="160"/>
-      <c r="J1" s="160"/>
-      <c r="K1" s="160"/>
-      <c r="L1" s="160"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
+      <c r="J1" s="158"/>
+      <c r="K1" s="158"/>
+      <c r="L1" s="158"/>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
       <c r="O1" s="5"/>
@@ -11698,22 +11682,22 @@
       <c r="Z1" s="5"/>
     </row>
     <row r="2" spans="1:26" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="161" t="s">
+      <c r="A2" s="159" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="160"/>
-      <c r="C2" s="160"/>
-      <c r="D2" s="160"/>
+      <c r="B2" s="158"/>
+      <c r="C2" s="158"/>
+      <c r="D2" s="158"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="162" t="s">
+      <c r="F2" s="160" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="152"/>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
-      <c r="J2" s="152"/>
-      <c r="K2" s="152"/>
-      <c r="L2" s="152"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="150"/>
+      <c r="I2" s="150"/>
+      <c r="J2" s="150"/>
+      <c r="K2" s="150"/>
+      <c r="L2" s="150"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
@@ -11749,13 +11733,13 @@
       <c r="G3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="163" t="s">
+      <c r="H3" s="161" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="152"/>
-      <c r="J3" s="152"/>
-      <c r="K3" s="152"/>
-      <c r="L3" s="153"/>
+      <c r="I3" s="150"/>
+      <c r="J3" s="150"/>
+      <c r="K3" s="150"/>
+      <c r="L3" s="151"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
@@ -11772,11 +11756,11 @@
       <c r="Z3" s="5"/>
     </row>
     <row r="4" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="155" t="s">
+      <c r="A4" s="153" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="152"/>
-      <c r="C4" s="153"/>
+      <c r="B4" s="150"/>
+      <c r="C4" s="151"/>
       <c r="D4" s="8" t="s">
         <v>28</v>
       </c>
@@ -12100,11 +12084,11 @@
       <c r="Z10" s="5"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="155" t="s">
+      <c r="A11" s="153" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="152"/>
-      <c r="C11" s="153"/>
+      <c r="B11" s="150"/>
+      <c r="C11" s="151"/>
       <c r="D11" s="8">
         <f>SUM(D5:D10)</f>
         <v>47</v>
@@ -12483,11 +12467,11 @@
       <c r="Z20" s="5"/>
     </row>
     <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="155" t="s">
+      <c r="A21" s="153" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="152"/>
-      <c r="C21" s="153"/>
+      <c r="B21" s="150"/>
+      <c r="C21" s="151"/>
       <c r="D21" s="8">
         <f>SUM(D12:D20)</f>
         <v>66</v>
@@ -13193,9 +13177,9 @@
       <c r="Z40" s="5"/>
     </row>
     <row r="41" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="156"/>
-      <c r="B41" s="152"/>
-      <c r="C41" s="153"/>
+      <c r="A41" s="154"/>
+      <c r="B41" s="150"/>
+      <c r="C41" s="151"/>
       <c r="D41" s="8">
         <f>SUM(D32:D40)</f>
         <v>65</v>
@@ -19650,19 +19634,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="172" t="s">
+      <c r="A1" s="162" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="160"/>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
-      <c r="E1" s="160"/>
-      <c r="F1" s="160"/>
-      <c r="G1" s="160"/>
-      <c r="H1" s="160"/>
-      <c r="I1" s="160"/>
-      <c r="J1" s="160"/>
-      <c r="K1" s="160"/>
+      <c r="B1" s="158"/>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
+      <c r="J1" s="158"/>
+      <c r="K1" s="158"/>
       <c r="L1" s="29"/>
       <c r="M1" s="29"/>
       <c r="N1" s="29"/>
@@ -20611,10 +20595,10 @@
       <c r="A33" s="30"/>
       <c r="B33" s="30"/>
       <c r="C33" s="30"/>
-      <c r="D33" s="173" t="s">
+      <c r="D33" s="163" t="s">
         <v>102</v>
       </c>
-      <c r="E33" s="153"/>
+      <c r="E33" s="151"/>
       <c r="F33" s="30"/>
       <c r="G33" s="30"/>
       <c r="H33" s="30"/>
@@ -20858,19 +20842,19 @@
       <c r="Z40" s="30"/>
     </row>
     <row r="41" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="174" t="s">
+      <c r="A41" s="164" t="s">
         <v>109</v>
       </c>
-      <c r="B41" s="152"/>
-      <c r="C41" s="152"/>
-      <c r="D41" s="152"/>
-      <c r="E41" s="152"/>
-      <c r="F41" s="152"/>
-      <c r="G41" s="152"/>
-      <c r="H41" s="152"/>
-      <c r="I41" s="152"/>
-      <c r="J41" s="152"/>
-      <c r="K41" s="153"/>
+      <c r="B41" s="150"/>
+      <c r="C41" s="150"/>
+      <c r="D41" s="150"/>
+      <c r="E41" s="150"/>
+      <c r="F41" s="150"/>
+      <c r="G41" s="150"/>
+      <c r="H41" s="150"/>
+      <c r="I41" s="150"/>
+      <c r="J41" s="150"/>
+      <c r="K41" s="151"/>
       <c r="L41" s="29"/>
       <c r="M41" s="29"/>
       <c r="N41" s="29"/>
@@ -20888,19 +20872,19 @@
       <c r="Z41" s="29"/>
     </row>
     <row r="42" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="175" t="s">
+      <c r="A42" s="165" t="s">
         <v>110</v>
       </c>
-      <c r="B42" s="152"/>
-      <c r="C42" s="152"/>
-      <c r="D42" s="152"/>
-      <c r="E42" s="152"/>
-      <c r="F42" s="152"/>
-      <c r="G42" s="152"/>
-      <c r="H42" s="152"/>
-      <c r="I42" s="152"/>
-      <c r="J42" s="152"/>
-      <c r="K42" s="153"/>
+      <c r="B42" s="150"/>
+      <c r="C42" s="150"/>
+      <c r="D42" s="150"/>
+      <c r="E42" s="150"/>
+      <c r="F42" s="150"/>
+      <c r="G42" s="150"/>
+      <c r="H42" s="150"/>
+      <c r="I42" s="150"/>
+      <c r="J42" s="150"/>
+      <c r="K42" s="151"/>
       <c r="L42" s="29"/>
       <c r="M42" s="29"/>
       <c r="N42" s="29"/>
@@ -20918,19 +20902,19 @@
       <c r="Z42" s="29"/>
     </row>
     <row r="43" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="176" t="s">
+      <c r="A43" s="166" t="s">
         <v>111</v>
       </c>
-      <c r="B43" s="152"/>
-      <c r="C43" s="152"/>
-      <c r="D43" s="152"/>
-      <c r="E43" s="152"/>
-      <c r="F43" s="152"/>
-      <c r="G43" s="152"/>
-      <c r="H43" s="152"/>
-      <c r="I43" s="152"/>
-      <c r="J43" s="152"/>
-      <c r="K43" s="153"/>
+      <c r="B43" s="150"/>
+      <c r="C43" s="150"/>
+      <c r="D43" s="150"/>
+      <c r="E43" s="150"/>
+      <c r="F43" s="150"/>
+      <c r="G43" s="150"/>
+      <c r="H43" s="150"/>
+      <c r="I43" s="150"/>
+      <c r="J43" s="150"/>
+      <c r="K43" s="151"/>
       <c r="L43" s="29"/>
       <c r="M43" s="29"/>
       <c r="N43" s="29"/>
@@ -20948,19 +20932,19 @@
       <c r="Z43" s="29"/>
     </row>
     <row r="44" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="169" t="s">
+      <c r="A44" s="167" t="s">
         <v>112</v>
       </c>
-      <c r="B44" s="152"/>
-      <c r="C44" s="152"/>
-      <c r="D44" s="152"/>
-      <c r="E44" s="152"/>
-      <c r="F44" s="152"/>
-      <c r="G44" s="152"/>
-      <c r="H44" s="152"/>
-      <c r="I44" s="152"/>
-      <c r="J44" s="152"/>
-      <c r="K44" s="153"/>
+      <c r="B44" s="150"/>
+      <c r="C44" s="150"/>
+      <c r="D44" s="150"/>
+      <c r="E44" s="150"/>
+      <c r="F44" s="150"/>
+      <c r="G44" s="150"/>
+      <c r="H44" s="150"/>
+      <c r="I44" s="150"/>
+      <c r="J44" s="150"/>
+      <c r="K44" s="151"/>
       <c r="L44" s="29"/>
       <c r="M44" s="29"/>
       <c r="N44" s="29"/>
@@ -21006,19 +20990,19 @@
       <c r="Z45" s="30"/>
     </row>
     <row r="46" spans="1:26" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="170" t="s">
+      <c r="A46" s="168" t="s">
         <v>113</v>
       </c>
-      <c r="B46" s="160"/>
-      <c r="C46" s="160"/>
-      <c r="D46" s="160"/>
-      <c r="E46" s="160"/>
-      <c r="F46" s="160"/>
-      <c r="G46" s="160"/>
-      <c r="H46" s="160"/>
-      <c r="I46" s="160"/>
-      <c r="J46" s="160"/>
-      <c r="K46" s="160"/>
+      <c r="B46" s="158"/>
+      <c r="C46" s="158"/>
+      <c r="D46" s="158"/>
+      <c r="E46" s="158"/>
+      <c r="F46" s="158"/>
+      <c r="G46" s="158"/>
+      <c r="H46" s="158"/>
+      <c r="I46" s="158"/>
+      <c r="J46" s="158"/>
+      <c r="K46" s="158"/>
       <c r="L46" s="30"/>
       <c r="M46" s="30"/>
       <c r="N46" s="30"/>
@@ -21040,17 +21024,17 @@
         <v>114</v>
       </c>
       <c r="B47" s="37"/>
-      <c r="C47" s="165" t="s">
+      <c r="C47" s="173" t="s">
         <v>115</v>
       </c>
-      <c r="D47" s="152"/>
-      <c r="E47" s="152"/>
-      <c r="F47" s="152"/>
-      <c r="G47" s="152"/>
-      <c r="H47" s="152"/>
-      <c r="I47" s="152"/>
-      <c r="J47" s="152"/>
-      <c r="K47" s="153"/>
+      <c r="D47" s="150"/>
+      <c r="E47" s="150"/>
+      <c r="F47" s="150"/>
+      <c r="G47" s="150"/>
+      <c r="H47" s="150"/>
+      <c r="I47" s="150"/>
+      <c r="J47" s="150"/>
+      <c r="K47" s="151"/>
       <c r="L47" s="38"/>
       <c r="M47" s="38"/>
       <c r="N47" s="38"/>
@@ -21068,31 +21052,31 @@
       <c r="Z47" s="38"/>
     </row>
     <row r="48" spans="1:26" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="166"/>
-      <c r="B48" s="168" t="s">
+      <c r="A48" s="174"/>
+      <c r="B48" s="169" t="s">
         <v>116</v>
       </c>
-      <c r="C48" s="168" t="s">
+      <c r="C48" s="169" t="s">
         <v>117</v>
       </c>
-      <c r="D48" s="168" t="s">
+      <c r="D48" s="169" t="s">
         <v>118</v>
       </c>
-      <c r="E48" s="168" t="s">
+      <c r="E48" s="169" t="s">
         <v>87</v>
       </c>
-      <c r="F48" s="168" t="s">
+      <c r="F48" s="169" t="s">
         <v>119</v>
       </c>
-      <c r="G48" s="168" t="s">
+      <c r="G48" s="169" t="s">
         <v>91</v>
       </c>
       <c r="H48" s="171" t="s">
         <v>120</v>
       </c>
-      <c r="I48" s="152"/>
-      <c r="J48" s="152"/>
-      <c r="K48" s="152"/>
+      <c r="I48" s="150"/>
+      <c r="J48" s="150"/>
+      <c r="K48" s="150"/>
       <c r="L48" s="39"/>
       <c r="M48" s="39"/>
       <c r="N48" s="39"/>
@@ -21110,17 +21094,17 @@
       <c r="Z48" s="39"/>
     </row>
     <row r="49" spans="1:26" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="167"/>
-      <c r="B49" s="167"/>
-      <c r="C49" s="167"/>
-      <c r="D49" s="167"/>
-      <c r="E49" s="167"/>
-      <c r="F49" s="167"/>
-      <c r="G49" s="167"/>
+      <c r="A49" s="170"/>
+      <c r="B49" s="170"/>
+      <c r="C49" s="170"/>
+      <c r="D49" s="170"/>
+      <c r="E49" s="170"/>
+      <c r="F49" s="170"/>
+      <c r="G49" s="170"/>
       <c r="H49" s="171" t="s">
         <v>121</v>
       </c>
-      <c r="I49" s="153"/>
+      <c r="I49" s="151"/>
       <c r="J49" s="40" t="s">
         <v>122</v>
       </c>
@@ -21166,10 +21150,10 @@
       <c r="G50" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="H50" s="164" t="s">
+      <c r="H50" s="172" t="s">
         <v>125</v>
       </c>
-      <c r="I50" s="153"/>
+      <c r="I50" s="151"/>
       <c r="J50" s="46" t="s">
         <v>126</v>
       </c>
@@ -21469,8 +21453,8 @@
         <v>#VALUE!</v>
       </c>
       <c r="G59" s="44"/>
-      <c r="H59" s="164"/>
-      <c r="I59" s="153"/>
+      <c r="H59" s="172"/>
+      <c r="I59" s="151"/>
       <c r="J59" s="46"/>
       <c r="K59" s="46"/>
       <c r="L59" s="39"/>
@@ -21500,8 +21484,8 @@
         <v>#VALUE!</v>
       </c>
       <c r="G60" s="44"/>
-      <c r="H60" s="164"/>
-      <c r="I60" s="153"/>
+      <c r="H60" s="172"/>
+      <c r="I60" s="151"/>
       <c r="J60" s="46"/>
       <c r="K60" s="46"/>
       <c r="L60" s="39"/>
@@ -27862,16 +27846,6 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="A41:K41"/>
-    <mergeCell ref="A42:K42"/>
-    <mergeCell ref="A43:K43"/>
-    <mergeCell ref="A44:K44"/>
-    <mergeCell ref="A46:K46"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="H48:K48"/>
-    <mergeCell ref="H49:I49"/>
     <mergeCell ref="H50:I50"/>
     <mergeCell ref="H59:I59"/>
     <mergeCell ref="H60:I60"/>
@@ -27882,15 +27856,25 @@
     <mergeCell ref="D48:D49"/>
     <mergeCell ref="E48:E49"/>
     <mergeCell ref="F48:F49"/>
+    <mergeCell ref="A44:K44"/>
+    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="H48:K48"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A42:K42"/>
+    <mergeCell ref="A43:K43"/>
   </mergeCells>
   <conditionalFormatting sqref="F50:F60">
-    <cfRule type="cellIs" dxfId="8" priority="1" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" stopIfTrue="1" operator="equal">
       <formula>$D$15</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="2" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="2" stopIfTrue="1" operator="equal">
       <formula>$D$16</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="3" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="3" stopIfTrue="1" operator="equal">
       <formula>$D$17</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27924,11 +27908,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="175" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="153"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="151"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -27982,11 +27966,11 @@
       <c r="Z2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="178" t="s">
+      <c r="A3" s="176" t="s">
         <v>133</v>
       </c>
-      <c r="B3" s="160"/>
-      <c r="C3" s="160"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="158"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -28352,11 +28336,11 @@
       <c r="Z13" s="1"/>
     </row>
     <row r="14" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="178" t="s">
+      <c r="A14" s="176" t="s">
         <v>148</v>
       </c>
-      <c r="B14" s="160"/>
-      <c r="C14" s="160"/>
+      <c r="B14" s="158"/>
+      <c r="C14" s="158"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -35047,19 +35031,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="11.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="172" t="s">
+      <c r="A1" s="162" t="s">
         <v>157</v>
       </c>
-      <c r="B1" s="160"/>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
-      <c r="E1" s="160"/>
-      <c r="F1" s="160"/>
-      <c r="G1" s="160"/>
-      <c r="H1" s="160"/>
-      <c r="I1" s="160"/>
-      <c r="J1" s="160"/>
-      <c r="K1" s="160"/>
+      <c r="B1" s="158"/>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
+      <c r="J1" s="158"/>
+      <c r="K1" s="158"/>
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
@@ -35077,23 +35061,23 @@
       <c r="Z1" s="5"/>
     </row>
     <row r="2" spans="1:26" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="179" t="s">
+      <c r="A2" s="177" t="s">
         <v>158</v>
       </c>
-      <c r="B2" s="152"/>
-      <c r="C2" s="152"/>
-      <c r="D2" s="153"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="151"/>
       <c r="E2" s="67">
         <f>Planejamento!$B$10</f>
         <v>386.4</v>
       </c>
       <c r="F2" s="68"/>
-      <c r="G2" s="179" t="s">
+      <c r="G2" s="177" t="s">
         <v>158</v>
       </c>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
-      <c r="J2" s="153"/>
+      <c r="H2" s="150"/>
+      <c r="I2" s="150"/>
+      <c r="J2" s="151"/>
       <c r="K2" s="67"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
@@ -35114,17 +35098,17 @@
     <row r="3" spans="1:26" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="69"/>
       <c r="B3" s="70"/>
-      <c r="C3" s="180" t="s">
+      <c r="C3" s="178" t="s">
         <v>159</v>
       </c>
-      <c r="D3" s="152"/>
-      <c r="E3" s="153"/>
+      <c r="D3" s="150"/>
+      <c r="E3" s="151"/>
       <c r="F3" s="71"/>
-      <c r="G3" s="181" t="s">
+      <c r="G3" s="179" t="s">
         <v>160</v>
       </c>
-      <c r="H3" s="152"/>
-      <c r="I3" s="153"/>
+      <c r="H3" s="150"/>
+      <c r="I3" s="151"/>
       <c r="J3" s="72"/>
       <c r="K3" s="73"/>
       <c r="L3" s="5"/>
@@ -35248,7 +35232,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="124" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C6" s="125">
         <v>45910</v>
@@ -35259,7 +35243,7 @@
       <c r="E6" s="126">
         <v>27</v>
       </c>
-      <c r="F6" s="127" t="s">
+      <c r="F6" s="121" t="s">
         <v>170</v>
       </c>
       <c r="G6" s="125">
@@ -35271,11 +35255,11 @@
       <c r="I6" s="126">
         <v>28</v>
       </c>
-      <c r="J6" s="128">
+      <c r="J6" s="127">
         <v>1</v>
       </c>
       <c r="K6" s="123" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
@@ -35297,35 +35281,35 @@
       <c r="A7" s="117">
         <v>3</v>
       </c>
-      <c r="B7" s="129" t="s">
-        <v>250</v>
-      </c>
-      <c r="C7" s="130" t="s">
+      <c r="B7" s="128" t="s">
+        <v>249</v>
+      </c>
+      <c r="C7" s="129" t="s">
         <v>172</v>
       </c>
-      <c r="D7" s="131">
+      <c r="D7" s="130">
         <v>45946</v>
       </c>
-      <c r="E7" s="130">
+      <c r="E7" s="129">
         <v>30</v>
       </c>
-      <c r="F7" s="132" t="s">
+      <c r="F7" s="121" t="s">
         <v>170</v>
       </c>
-      <c r="G7" s="133">
+      <c r="G7" s="131">
         <v>45930</v>
       </c>
-      <c r="H7" s="133">
+      <c r="H7" s="131">
         <v>45951</v>
       </c>
-      <c r="I7" s="134">
+      <c r="I7" s="132">
         <v>35</v>
       </c>
-      <c r="J7" s="128">
+      <c r="J7" s="127">
         <v>-5</v>
       </c>
       <c r="K7" s="123" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
@@ -35347,35 +35331,35 @@
       <c r="A8" s="117">
         <v>4</v>
       </c>
-      <c r="B8" s="129" t="s">
+      <c r="B8" s="128" t="s">
+        <v>250</v>
+      </c>
+      <c r="C8" s="130">
+        <v>45926</v>
+      </c>
+      <c r="D8" s="130">
+        <v>45946</v>
+      </c>
+      <c r="E8" s="129">
+        <v>30</v>
+      </c>
+      <c r="F8" s="121" t="s">
+        <v>170</v>
+      </c>
+      <c r="G8" s="131">
+        <v>45930</v>
+      </c>
+      <c r="H8" s="133">
+        <v>45951</v>
+      </c>
+      <c r="I8" s="134">
+        <v>37</v>
+      </c>
+      <c r="J8" s="135">
+        <v>-7</v>
+      </c>
+      <c r="K8" s="136" t="s">
         <v>251</v>
-      </c>
-      <c r="C8" s="131">
-        <v>45926</v>
-      </c>
-      <c r="D8" s="131">
-        <v>45946</v>
-      </c>
-      <c r="E8" s="130">
-        <v>30</v>
-      </c>
-      <c r="F8" s="132" t="s">
-        <v>170</v>
-      </c>
-      <c r="G8" s="133">
-        <v>45930</v>
-      </c>
-      <c r="H8" s="135">
-        <v>45951</v>
-      </c>
-      <c r="I8" s="136">
-        <v>33</v>
-      </c>
-      <c r="J8" s="137">
-        <v>-3</v>
-      </c>
-      <c r="K8" s="138" t="s">
-        <v>253</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
@@ -35397,28 +35381,36 @@
       <c r="A9" s="117">
         <v>5</v>
       </c>
-      <c r="B9" s="129" t="s">
-        <v>174</v>
-      </c>
-      <c r="C9" s="131">
+      <c r="B9" s="128" t="s">
+        <v>173</v>
+      </c>
+      <c r="C9" s="130">
         <v>45972</v>
       </c>
-      <c r="D9" s="131">
+      <c r="D9" s="130">
         <v>45981</v>
       </c>
-      <c r="E9" s="130">
+      <c r="E9" s="129">
         <v>5</v>
       </c>
-      <c r="F9" s="132" t="s">
-        <v>173</v>
-      </c>
-      <c r="G9" s="135">
-        <v>45946</v>
-      </c>
-      <c r="H9" s="135"/>
-      <c r="I9" s="136"/>
-      <c r="J9" s="137"/>
-      <c r="K9" s="139"/>
+      <c r="F9" s="121" t="s">
+        <v>170</v>
+      </c>
+      <c r="G9" s="133">
+        <v>45972</v>
+      </c>
+      <c r="H9" s="133">
+        <v>45983</v>
+      </c>
+      <c r="I9" s="134">
+        <v>6</v>
+      </c>
+      <c r="J9" s="135">
+        <v>-1</v>
+      </c>
+      <c r="K9" s="137">
+        <v>2</v>
+      </c>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
@@ -35439,16 +35431,16 @@
       <c r="A10" s="117">
         <v>6</v>
       </c>
-      <c r="B10" s="140"/>
-      <c r="C10" s="141"/>
-      <c r="D10" s="141"/>
-      <c r="E10" s="142"/>
-      <c r="F10" s="143"/>
-      <c r="G10" s="144"/>
-      <c r="H10" s="144"/>
-      <c r="I10" s="145"/>
-      <c r="J10" s="146"/>
-      <c r="K10" s="139"/>
+      <c r="B10" s="138"/>
+      <c r="C10" s="139"/>
+      <c r="D10" s="139"/>
+      <c r="E10" s="140"/>
+      <c r="F10" s="141"/>
+      <c r="G10" s="142"/>
+      <c r="H10" s="142"/>
+      <c r="I10" s="143"/>
+      <c r="J10" s="144"/>
+      <c r="K10" s="137"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
@@ -35469,16 +35461,16 @@
       <c r="A11" s="117">
         <v>7</v>
       </c>
-      <c r="B11" s="147"/>
+      <c r="B11" s="145"/>
       <c r="C11" s="119"/>
       <c r="D11" s="119"/>
-      <c r="E11" s="148"/>
-      <c r="F11" s="149"/>
-      <c r="G11" s="144"/>
-      <c r="H11" s="144"/>
-      <c r="I11" s="145"/>
-      <c r="J11" s="146"/>
-      <c r="K11" s="139"/>
+      <c r="E11" s="146"/>
+      <c r="F11" s="147"/>
+      <c r="G11" s="142"/>
+      <c r="H11" s="142"/>
+      <c r="I11" s="143"/>
+      <c r="J11" s="144"/>
+      <c r="K11" s="137"/>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
@@ -35499,16 +35491,16 @@
       <c r="A12" s="117">
         <v>8</v>
       </c>
-      <c r="B12" s="150"/>
-      <c r="C12" s="144"/>
-      <c r="D12" s="144"/>
-      <c r="E12" s="145"/>
-      <c r="F12" s="149"/>
-      <c r="G12" s="144"/>
-      <c r="H12" s="144"/>
-      <c r="I12" s="145"/>
-      <c r="J12" s="146"/>
-      <c r="K12" s="139"/>
+      <c r="B12" s="148"/>
+      <c r="C12" s="142"/>
+      <c r="D12" s="142"/>
+      <c r="E12" s="143"/>
+      <c r="F12" s="147"/>
+      <c r="G12" s="142"/>
+      <c r="H12" s="142"/>
+      <c r="I12" s="143"/>
+      <c r="J12" s="144"/>
+      <c r="K12" s="137"/>
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
@@ -35529,16 +35521,16 @@
       <c r="A13" s="117">
         <v>9</v>
       </c>
-      <c r="B13" s="150"/>
-      <c r="C13" s="144"/>
-      <c r="D13" s="144"/>
-      <c r="E13" s="145"/>
-      <c r="F13" s="149"/>
-      <c r="G13" s="144"/>
-      <c r="H13" s="144"/>
-      <c r="I13" s="145"/>
-      <c r="J13" s="146"/>
-      <c r="K13" s="139"/>
+      <c r="B13" s="148"/>
+      <c r="C13" s="142"/>
+      <c r="D13" s="142"/>
+      <c r="E13" s="143"/>
+      <c r="F13" s="147"/>
+      <c r="G13" s="142"/>
+      <c r="H13" s="142"/>
+      <c r="I13" s="143"/>
+      <c r="J13" s="144"/>
+      <c r="K13" s="137"/>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
@@ -35559,16 +35551,16 @@
       <c r="A14" s="117">
         <v>10</v>
       </c>
-      <c r="B14" s="150"/>
-      <c r="C14" s="144"/>
-      <c r="D14" s="144"/>
-      <c r="E14" s="145"/>
-      <c r="F14" s="149"/>
-      <c r="G14" s="144"/>
-      <c r="H14" s="144"/>
-      <c r="I14" s="145"/>
-      <c r="J14" s="146"/>
-      <c r="K14" s="139"/>
+      <c r="B14" s="148"/>
+      <c r="C14" s="142"/>
+      <c r="D14" s="142"/>
+      <c r="E14" s="143"/>
+      <c r="F14" s="147"/>
+      <c r="G14" s="142"/>
+      <c r="H14" s="142"/>
+      <c r="I14" s="143"/>
+      <c r="J14" s="144"/>
+      <c r="K14" s="137"/>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
@@ -35599,11 +35591,11 @@
       <c r="H15" s="113"/>
       <c r="I15" s="115">
         <f t="shared" ref="I15:J15" si="0">SUM(I5:I14)</f>
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="J15" s="116">
         <f t="shared" si="0"/>
-        <v>-4</v>
+        <v>-9</v>
       </c>
       <c r="K15" s="113"/>
       <c r="L15" s="5"/>
@@ -42151,33 +42143,38 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:D5 A6:A9 A10:D14">
-    <cfRule type="expression" dxfId="5" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="3" stopIfTrue="1">
       <formula>$F5="Ongoing"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
       <formula>OR($F5="Planned",$F5="Unplanned")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5 F10:F14">
-    <cfRule type="cellIs" dxfId="3" priority="1" stopIfTrue="1" operator="equal">
+  <conditionalFormatting sqref="F5:F14">
+    <cfRule type="cellIs" dxfId="4" priority="2" stopIfTrue="1" operator="equal">
       <formula>"Unplanned"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="6" stopIfTrue="1">
       <formula>$F5="Planned"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:H5 F10:H14">
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="4" stopIfTrue="1">
       <formula>$F5="Ongoing"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:H5 G10:H14">
-    <cfRule type="expression" dxfId="0" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="8" stopIfTrue="1">
       <formula>OR($F5="Planned",$F5="Unplanned")</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F6:F9">
+    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
+      <formula>$F6="Ongoing"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F5 F10:F14" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F5:F14" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Planejado,Em execução,Entregue,Não planejado"</formula1>
     </dataValidation>
   </dataValidations>
@@ -42210,22 +42207,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="184" t="s">
-        <v>175</v>
-      </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
-      <c r="G1" s="152"/>
-      <c r="H1" s="152"/>
-      <c r="I1" s="152"/>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="152"/>
-      <c r="M1" s="152"/>
-      <c r="N1" s="153"/>
+      <c r="A1" s="182" t="s">
+        <v>174</v>
+      </c>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="151"/>
       <c r="O1" s="29"/>
       <c r="P1" s="29"/>
       <c r="Q1" s="29"/>
@@ -42240,22 +42237,22 @@
       <c r="Z1" s="29"/>
     </row>
     <row r="2" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="185" t="s">
+      <c r="A2" s="183" t="s">
         <v>109</v>
       </c>
-      <c r="B2" s="152"/>
-      <c r="C2" s="152"/>
-      <c r="D2" s="152"/>
-      <c r="E2" s="152"/>
-      <c r="F2" s="152"/>
-      <c r="G2" s="152"/>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
-      <c r="J2" s="152"/>
-      <c r="K2" s="152"/>
-      <c r="L2" s="152"/>
-      <c r="M2" s="152"/>
-      <c r="N2" s="153"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="150"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="150"/>
+      <c r="I2" s="150"/>
+      <c r="J2" s="150"/>
+      <c r="K2" s="150"/>
+      <c r="L2" s="150"/>
+      <c r="M2" s="150"/>
+      <c r="N2" s="151"/>
       <c r="O2" s="76"/>
       <c r="P2" s="76"/>
       <c r="Q2" s="76"/>
@@ -42270,22 +42267,22 @@
       <c r="Z2" s="76"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="186" t="s">
-        <v>176</v>
-      </c>
-      <c r="B3" s="152"/>
-      <c r="C3" s="152"/>
-      <c r="D3" s="152"/>
-      <c r="E3" s="152"/>
-      <c r="F3" s="152"/>
-      <c r="G3" s="152"/>
-      <c r="H3" s="152"/>
-      <c r="I3" s="152"/>
-      <c r="J3" s="152"/>
-      <c r="K3" s="152"/>
-      <c r="L3" s="152"/>
-      <c r="M3" s="152"/>
-      <c r="N3" s="153"/>
+      <c r="A3" s="184" t="s">
+        <v>175</v>
+      </c>
+      <c r="B3" s="150"/>
+      <c r="C3" s="150"/>
+      <c r="D3" s="150"/>
+      <c r="E3" s="150"/>
+      <c r="F3" s="150"/>
+      <c r="G3" s="150"/>
+      <c r="H3" s="150"/>
+      <c r="I3" s="150"/>
+      <c r="J3" s="150"/>
+      <c r="K3" s="150"/>
+      <c r="L3" s="150"/>
+      <c r="M3" s="150"/>
+      <c r="N3" s="151"/>
       <c r="O3" s="76"/>
       <c r="P3" s="76"/>
       <c r="Q3" s="76"/>
@@ -42300,22 +42297,22 @@
       <c r="Z3" s="76"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="187" t="s">
-        <v>177</v>
-      </c>
-      <c r="B4" s="152"/>
-      <c r="C4" s="152"/>
-      <c r="D4" s="152"/>
-      <c r="E4" s="152"/>
-      <c r="F4" s="152"/>
-      <c r="G4" s="152"/>
-      <c r="H4" s="152"/>
-      <c r="I4" s="152"/>
-      <c r="J4" s="152"/>
-      <c r="K4" s="152"/>
-      <c r="L4" s="152"/>
-      <c r="M4" s="152"/>
-      <c r="N4" s="153"/>
+      <c r="A4" s="185" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="150"/>
+      <c r="C4" s="150"/>
+      <c r="D4" s="150"/>
+      <c r="E4" s="150"/>
+      <c r="F4" s="150"/>
+      <c r="G4" s="150"/>
+      <c r="H4" s="150"/>
+      <c r="I4" s="150"/>
+      <c r="J4" s="150"/>
+      <c r="K4" s="150"/>
+      <c r="L4" s="150"/>
+      <c r="M4" s="150"/>
+      <c r="N4" s="151"/>
       <c r="O4" s="76"/>
       <c r="P4" s="76"/>
       <c r="Q4" s="76"/>
@@ -42330,22 +42327,22 @@
       <c r="Z4" s="76"/>
     </row>
     <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="188" t="s">
-        <v>178</v>
-      </c>
-      <c r="B5" s="152"/>
-      <c r="C5" s="152"/>
-      <c r="D5" s="152"/>
-      <c r="E5" s="152"/>
-      <c r="F5" s="152"/>
-      <c r="G5" s="152"/>
-      <c r="H5" s="152"/>
-      <c r="I5" s="152"/>
-      <c r="J5" s="152"/>
-      <c r="K5" s="152"/>
-      <c r="L5" s="152"/>
-      <c r="M5" s="152"/>
-      <c r="N5" s="153"/>
+      <c r="A5" s="186" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" s="150"/>
+      <c r="C5" s="150"/>
+      <c r="D5" s="150"/>
+      <c r="E5" s="150"/>
+      <c r="F5" s="150"/>
+      <c r="G5" s="150"/>
+      <c r="H5" s="150"/>
+      <c r="I5" s="150"/>
+      <c r="J5" s="150"/>
+      <c r="K5" s="150"/>
+      <c r="L5" s="150"/>
+      <c r="M5" s="150"/>
+      <c r="N5" s="151"/>
       <c r="O5" s="76"/>
       <c r="P5" s="76"/>
       <c r="Q5" s="76"/>
@@ -42388,28 +42385,28 @@
       <c r="Z6" s="5"/>
     </row>
     <row r="7" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="182" t="s">
+      <c r="A7" s="180" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" s="151"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="180" t="s">
         <v>179</v>
       </c>
-      <c r="B7" s="153"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="182" t="s">
+      <c r="E7" s="151"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="180" t="s">
         <v>180</v>
       </c>
-      <c r="E7" s="153"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="182" t="s">
+      <c r="H7" s="150"/>
+      <c r="I7" s="150"/>
+      <c r="J7" s="150"/>
+      <c r="K7" s="151"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="180" t="s">
         <v>181</v>
       </c>
-      <c r="H7" s="152"/>
-      <c r="I7" s="152"/>
-      <c r="J7" s="152"/>
-      <c r="K7" s="153"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="182" t="s">
-        <v>182</v>
-      </c>
-      <c r="N7" s="153"/>
+      <c r="N7" s="151"/>
       <c r="O7" s="5"/>
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
@@ -42425,40 +42422,40 @@
     </row>
     <row r="8" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="77" t="s">
+        <v>182</v>
+      </c>
+      <c r="B8" s="78" t="s">
         <v>183</v>
-      </c>
-      <c r="B8" s="78" t="s">
-        <v>184</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="77" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E8" s="78" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="77" t="s">
+        <v>185</v>
+      </c>
+      <c r="H8" s="77" t="s">
         <v>186</v>
-      </c>
-      <c r="H8" s="77" t="s">
-        <v>187</v>
       </c>
       <c r="I8" s="77" t="s">
         <v>85</v>
       </c>
       <c r="J8" s="78" t="s">
+        <v>187</v>
+      </c>
+      <c r="K8" s="78" t="s">
         <v>188</v>
-      </c>
-      <c r="K8" s="78" t="s">
-        <v>189</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="78" t="s">
+        <v>189</v>
+      </c>
+      <c r="N8" s="78" t="s">
         <v>190</v>
-      </c>
-      <c r="N8" s="78" t="s">
-        <v>191</v>
       </c>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
@@ -42475,21 +42472,21 @@
     </row>
     <row r="9" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="79" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="80" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="79" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E9" s="80" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="77" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H9" s="79">
         <v>2</v>
@@ -42506,7 +42503,7 @@
       </c>
       <c r="L9" s="5"/>
       <c r="M9" s="81" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N9" s="82"/>
       <c r="O9" s="5"/>
@@ -42524,17 +42521,17 @@
     </row>
     <row r="10" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="79" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B10" s="80" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="79"/>
       <c r="E10" s="80"/>
       <c r="F10" s="5"/>
       <c r="G10" s="77" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H10" s="79"/>
       <c r="I10" s="79"/>
@@ -42545,7 +42542,7 @@
       </c>
       <c r="L10" s="5"/>
       <c r="M10" s="81" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N10" s="82"/>
       <c r="O10" s="5"/>
@@ -42568,16 +42565,16 @@
       <c r="D11" s="79"/>
       <c r="E11" s="80"/>
       <c r="F11" s="5"/>
-      <c r="G11" s="182" t="s">
-        <v>199</v>
-      </c>
-      <c r="H11" s="152"/>
-      <c r="I11" s="152"/>
-      <c r="J11" s="152"/>
-      <c r="K11" s="153"/>
+      <c r="G11" s="180" t="s">
+        <v>198</v>
+      </c>
+      <c r="H11" s="150"/>
+      <c r="I11" s="150"/>
+      <c r="J11" s="150"/>
+      <c r="K11" s="151"/>
       <c r="L11" s="5"/>
       <c r="M11" s="81" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N11" s="82"/>
       <c r="O11" s="5"/>
@@ -42601,23 +42598,23 @@
       <c r="E12" s="80"/>
       <c r="F12" s="5"/>
       <c r="G12" s="77" t="s">
+        <v>185</v>
+      </c>
+      <c r="H12" s="77" t="s">
         <v>186</v>
-      </c>
-      <c r="H12" s="77" t="s">
-        <v>187</v>
       </c>
       <c r="I12" s="77" t="s">
         <v>85</v>
       </c>
       <c r="J12" s="78" t="s">
+        <v>187</v>
+      </c>
+      <c r="K12" s="78" t="s">
         <v>188</v>
-      </c>
-      <c r="K12" s="78" t="s">
-        <v>189</v>
       </c>
       <c r="L12" s="5"/>
       <c r="M12" s="81" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N12" s="82"/>
       <c r="O12" s="5"/>
@@ -42641,7 +42638,7 @@
       <c r="E13" s="80"/>
       <c r="F13" s="5"/>
       <c r="G13" s="77" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H13" s="79">
         <v>1</v>
@@ -42654,7 +42651,7 @@
       </c>
       <c r="L13" s="5"/>
       <c r="M13" s="81" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N13" s="82"/>
       <c r="O13" s="5"/>
@@ -42666,7 +42663,7 @@
       <c r="U13" s="5"/>
       <c r="V13" s="5"/>
       <c r="W13" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="X13" s="5"/>
       <c r="Y13" s="5"/>
@@ -42680,7 +42677,7 @@
       <c r="E14" s="80"/>
       <c r="F14" s="5"/>
       <c r="G14" s="77" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H14" s="79"/>
       <c r="I14" s="79"/>
@@ -42691,7 +42688,7 @@
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="81" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N14" s="82"/>
       <c r="O14" s="5"/>
@@ -42715,7 +42712,7 @@
       <c r="E15" s="80"/>
       <c r="F15" s="5"/>
       <c r="G15" s="77" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H15" s="79">
         <v>1</v>
@@ -42728,7 +42725,7 @@
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="81" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="N15" s="82"/>
       <c r="O15" s="5"/>
@@ -42751,19 +42748,19 @@
       <c r="D16" s="79"/>
       <c r="E16" s="80"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="183" t="s">
-        <v>209</v>
-      </c>
-      <c r="H16" s="152"/>
-      <c r="I16" s="152"/>
-      <c r="J16" s="153"/>
+      <c r="G16" s="181" t="s">
+        <v>208</v>
+      </c>
+      <c r="H16" s="150"/>
+      <c r="I16" s="150"/>
+      <c r="J16" s="151"/>
       <c r="K16" s="83">
         <f>SUM(K9,K10,K13,K14,K15)</f>
         <v>14</v>
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="81" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="N16" s="82"/>
       <c r="O16" s="5"/>
@@ -42793,7 +42790,7 @@
       <c r="K17" s="5"/>
       <c r="L17" s="5"/>
       <c r="M17" s="81" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N17" s="82"/>
       <c r="O17" s="5"/>
@@ -42823,7 +42820,7 @@
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
       <c r="M18" s="81" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N18" s="82"/>
       <c r="O18" s="5"/>
@@ -42853,7 +42850,7 @@
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
       <c r="M19" s="81" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="N19" s="82"/>
       <c r="O19" s="5"/>
@@ -42883,7 +42880,7 @@
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
       <c r="M20" s="81" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N20" s="82"/>
       <c r="O20" s="5"/>
@@ -42913,7 +42910,7 @@
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
       <c r="M21" s="81" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="N21" s="82"/>
       <c r="O21" s="5"/>
@@ -42943,7 +42940,7 @@
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
       <c r="M22" s="81" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N22" s="82"/>
       <c r="O22" s="5"/>
@@ -42973,7 +42970,7 @@
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
       <c r="M23" s="84" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N23" s="85">
         <f>SUM(N9:N22)</f>
@@ -43006,7 +43003,7 @@
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="84" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N24" s="83">
         <f>(N23*0.01)+0.65</f>
@@ -43039,7 +43036,7 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="84" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N25" s="86">
         <f>K16*N24</f>
@@ -43072,7 +43069,7 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="84" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N26" s="87">
         <v>19</v>
@@ -43104,7 +43101,7 @@
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="88" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="N27" s="89">
         <f>N25*N26</f>
@@ -49548,22 +49545,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="182" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
-      <c r="G1" s="152"/>
-      <c r="H1" s="152"/>
-      <c r="I1" s="152"/>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="152"/>
-      <c r="M1" s="152"/>
-      <c r="N1" s="153"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="151"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
@@ -49606,24 +49603,24 @@
       <c r="Z2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="189" t="s">
+      <c r="A3" s="187" t="s">
         <v>133</v>
       </c>
-      <c r="B3" s="160"/>
-      <c r="C3" s="160"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="158"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="189" t="s">
-        <v>222</v>
-      </c>
-      <c r="F3" s="160"/>
-      <c r="G3" s="160"/>
-      <c r="H3" s="160"/>
-      <c r="I3" s="160"/>
-      <c r="J3" s="160"/>
-      <c r="K3" s="160"/>
-      <c r="L3" s="160"/>
-      <c r="M3" s="160"/>
-      <c r="N3" s="160"/>
+      <c r="E3" s="187" t="s">
+        <v>221</v>
+      </c>
+      <c r="F3" s="158"/>
+      <c r="G3" s="158"/>
+      <c r="H3" s="158"/>
+      <c r="I3" s="158"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="158"/>
+      <c r="M3" s="158"/>
+      <c r="N3" s="158"/>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
@@ -49639,7 +49636,7 @@
     </row>
     <row r="4" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="90" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B4" s="91">
         <f>'#Estimativa-APF#'!$N$27</f>
@@ -49649,25 +49646,25 @@
         <v>135</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="190" t="s">
-        <v>224</v>
-      </c>
-      <c r="F4" s="192" t="s">
+      <c r="E4" s="189" t="s">
+        <v>223</v>
+      </c>
+      <c r="F4" s="188" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="153"/>
-      <c r="H4" s="192" t="s">
+      <c r="G4" s="151"/>
+      <c r="H4" s="188" t="s">
         <v>46</v>
       </c>
-      <c r="I4" s="153"/>
-      <c r="J4" s="192" t="s">
+      <c r="I4" s="151"/>
+      <c r="J4" s="188" t="s">
         <v>56</v>
       </c>
-      <c r="K4" s="153"/>
-      <c r="L4" s="192" t="s">
+      <c r="K4" s="151"/>
+      <c r="L4" s="188" t="s">
         <v>63</v>
       </c>
-      <c r="M4" s="153"/>
+      <c r="M4" s="151"/>
       <c r="N4" s="92"/>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
@@ -49690,28 +49687,28 @@
         <v>0</v>
       </c>
       <c r="C5" s="62" t="s">
+        <v>224</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="190"/>
+      <c r="F5" s="188" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="151"/>
+      <c r="H5" s="188" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="151"/>
+      <c r="J5" s="188" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" s="151"/>
+      <c r="L5" s="188" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" s="151"/>
+      <c r="N5" s="64" t="s">
         <v>225</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="191"/>
-      <c r="F5" s="192" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="153"/>
-      <c r="H5" s="192" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="153"/>
-      <c r="J5" s="192" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" s="153"/>
-      <c r="L5" s="192" t="s">
-        <v>28</v>
-      </c>
-      <c r="M5" s="153"/>
-      <c r="N5" s="64" t="s">
-        <v>226</v>
       </c>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
@@ -49728,7 +49725,7 @@
     </row>
     <row r="6" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="93" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B6" s="94">
         <f>B4+(B4*B5)</f>
@@ -49738,7 +49735,7 @@
         <v>135</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="167"/>
+      <c r="E6" s="170"/>
       <c r="F6" s="95">
         <f>B6*G6</f>
         <v>8.6450000000000014</v>
@@ -49783,7 +49780,7 @@
     </row>
     <row r="7" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="54" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B7" s="55">
         <v>1</v>
@@ -49791,7 +49788,7 @@
       <c r="C7" s="54"/>
       <c r="D7" s="1"/>
       <c r="E7" s="96" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F7" s="95">
         <f>F6*G7</f>
@@ -49840,17 +49837,17 @@
     </row>
     <row r="8" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="54" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B8" s="55">
         <v>40</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="96" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F8" s="95">
         <f>F6*G8</f>
@@ -49899,7 +49896,7 @@
     </row>
     <row r="9" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="54" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B9" s="55">
         <v>2</v>
@@ -49909,7 +49906,7 @@
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="96" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F9" s="95">
         <f>F6*G9</f>
@@ -49958,7 +49955,7 @@
     </row>
     <row r="10" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="98" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B10" s="99">
         <f>(B7*B8)*B9</f>
@@ -49969,7 +49966,7 @@
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="96" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F10" s="95">
         <f>F6*G10</f>
@@ -50018,7 +50015,7 @@
     </row>
     <row r="11" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="90" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B11" s="100">
         <f>B6/B10*2</f>
@@ -50029,7 +50026,7 @@
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="96" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F11" s="95">
         <f>F6*G11</f>
@@ -50078,7 +50075,7 @@
     </row>
     <row r="12" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="90" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B12" s="100">
         <f>B11/4</f>
@@ -50089,7 +50086,7 @@
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="101" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F12" s="102">
         <f t="shared" ref="F12:M12" si="1">SUM(F7:F11)</f>
@@ -50139,18 +50136,18 @@
     </row>
     <row r="13" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="98" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B13" s="104">
         <f>B11/B9</f>
         <v>2.1612499999999999</v>
       </c>
       <c r="C13" s="98" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="96" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F13" s="95">
         <f>F6*G13</f>
@@ -50203,7 +50200,7 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="96" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F14" s="95">
         <f>F6*G14</f>
@@ -50256,7 +50253,7 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="101" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F15" s="102">
         <f t="shared" ref="F15:M15" si="3">SUM(F13:F14)</f>
@@ -50305,14 +50302,14 @@
       <c r="Z15" s="1"/>
     </row>
     <row r="16" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="189" t="s">
+      <c r="A16" s="187" t="s">
         <v>148</v>
       </c>
-      <c r="B16" s="160"/>
-      <c r="C16" s="160"/>
+      <c r="B16" s="158"/>
+      <c r="C16" s="158"/>
       <c r="D16" s="1"/>
       <c r="E16" s="64" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F16" s="105">
         <f t="shared" ref="F16:M16" si="4">F12+F15</f>
@@ -50495,7 +50492,7 @@
     </row>
     <row r="21" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="50" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B21" s="109">
         <f>B18+B20</f>
@@ -50593,7 +50590,7 @@
     </row>
     <row r="24" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="50" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B24" s="109">
         <f>B21+B23</f>
